--- a/outputs/pivot_summary.xlsx
+++ b/outputs/pivot_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayubi\Downloads\ayushkumar_bitsom_ba_2511507_part1_data_cleaning\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5910A6D7-3E1F-4161-AB65-B4B90F73B8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CD3AD2-26F1-4916-BB17-2A581A8BB787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="25" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -175,7 +175,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -206,95 +206,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="172" formatCode="0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="0.0"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="171" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="170" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="168" formatCode="0.0000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="0.00000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.000"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -35284,7 +35226,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EDE61CF-0387-46B7-9836-0E8C6AC089C8}" name="PivotTable8" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EDE61CF-0387-46B7-9836-0E8C6AC089C8}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:C9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField showAll="0"/>
@@ -35381,7 +35323,7 @@
     <dataField name="Average of calculated_profit" fld="28" subtotal="average" baseField="10" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="22">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -35398,7 +35340,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F3F29D9-F0CA-46B4-85C4-64CBDD6AFBB4}" name="PivotTable9" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F3F29D9-F0CA-46B4-85C4-64CBDD6AFBB4}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:D20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField showAll="0"/>
@@ -35415,13 +35357,22 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
         <item x="2"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="14">
@@ -35474,6 +35425,21 @@
   </rowFields>
   <rowItems count="17">
     <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i>
       <x/>
     </i>
     <i r="1">
@@ -35506,21 +35472,6 @@
     <i r="1">
       <x v="11"/>
     </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -35548,7 +35499,7 @@
     <dataField name="Average of profit_margin" fld="29" subtotal="average" baseField="14" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="20">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -35565,7 +35516,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{451DE46A-7E6A-4DEB-A031-C62D6E51DCDE}" name="PivotTable10" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{451DE46A-7E6A-4DEB-A031-C62D6E51DCDE}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="35">
     <pivotField dataField="1" showAll="0"/>
@@ -35652,7 +35603,7 @@
     <dataField name="Average of Shipping_delay_days" fld="6" subtotal="average" baseField="17" baseItem="0" numFmtId="1"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -35675,7 +35626,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1057FCEB-BA4C-4677-9C83-A0F2DA96DC33}" name="PivotTable11" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1057FCEB-BA4C-4677-9C83-A0F2DA96DC33}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField showAll="0"/>
@@ -35687,7 +35638,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="5">
         <item x="0"/>
         <item x="2"/>
@@ -35695,6 +35646,15 @@
         <item x="1"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -35734,16 +35694,16 @@
   </rowFields>
   <rowItems count="5">
     <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
+      <x v="3"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="3"/>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -35789,7 +35749,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3F6A9D6-CAA0-4DCD-98E3-440553933D4C}" name="PivotTable12" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F3F6A9D6-CAA0-4DCD-98E3-440553933D4C}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A1:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="35">
     <pivotField dataField="1" showAll="0"/>
@@ -35900,7 +35860,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{584394B1-871B-4963-9B78-CAF51188B08E}" name="PivotTable13" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{584394B1-871B-4963-9B78-CAF51188B08E}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:C30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField dataField="1" showAll="0">
@@ -36974,7 +36934,7 @@
     <pageField fld="31" hier="-1"/>
   </pageFields>
   <dataFields count="2">
-    <dataField name="Sum of calculated_sales" fld="25" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Sum of calculated_sales" fld="25" baseField="0" baseItem="0" numFmtId="164"/>
     <dataField name="Count of order_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
@@ -37001,7 +36961,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C5B41D9-08D4-4855-AFD7-39FB548501DA}" name="PivotTable14" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0C5B41D9-08D4-4855-AFD7-39FB548501DA}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField dataField="1" showAll="0"/>
@@ -37392,10 +37352,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>190747.34669999999</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>7426.8924578947372</v>
       </c>
     </row>
@@ -37403,10 +37363,10 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>1382236.5107999998</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>6963.870676510066</v>
       </c>
     </row>
@@ -37414,10 +37374,10 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>1298807.4690000005</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>7879.3165038759671</v>
       </c>
     </row>
@@ -37425,10 +37385,10 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>1554249.6489999997</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>7792.8767254901959</v>
       </c>
     </row>
@@ -37436,10 +37396,10 @@
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>1514069.3298999993</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>7577.9061032467516</v>
       </c>
     </row>
@@ -37447,10 +37407,10 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>5940110.3054000083</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>7540.5086016556252</v>
       </c>
     </row>
@@ -37494,239 +37454,239 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
-      <c r="B4" s="6">
-        <v>1920809.3479999998</v>
+      <c r="B4" s="5">
+        <v>2163307.7248999993</v>
       </c>
-      <c r="C4" s="6">
-        <v>1474211.1780000001</v>
+      <c r="C4" s="5">
+        <v>1682986.8349000006</v>
       </c>
-      <c r="D4" s="6">
-        <v>0.62356556552047815</v>
+      <c r="D4" s="5">
+        <v>0.60108244336540084</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>15</v>
+      <c r="A5" s="3" t="s">
+        <v>24</v>
       </c>
-      <c r="B5" s="6">
-        <v>410143.26149999996</v>
+      <c r="B5" s="5">
+        <v>520097.44449999998</v>
       </c>
-      <c r="C5" s="6">
-        <v>302771.12150000007</v>
+      <c r="C5" s="5">
+        <v>409532.86449999997</v>
       </c>
-      <c r="D5" s="6">
-        <v>0.55652151687548412</v>
+      <c r="D5" s="5">
+        <v>0.6452731666056164</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>16</v>
+      <c r="A6" s="3" t="s">
+        <v>25</v>
       </c>
-      <c r="B6" s="6">
-        <v>586817.53269999998</v>
+      <c r="B6" s="5">
+        <v>670579.78079999995</v>
       </c>
-      <c r="C6" s="6">
-        <v>454458.99270000012</v>
+      <c r="C6" s="5">
+        <v>525594.26080000005</v>
       </c>
-      <c r="D6" s="6">
-        <v>0.65342835477270822</v>
+      <c r="D6" s="5">
+        <v>0.62905170690821843</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
+      <c r="A7" s="3" t="s">
+        <v>26</v>
       </c>
-      <c r="B7" s="6">
-        <v>503663.22480000008</v>
+      <c r="B7" s="5">
+        <v>399429.75600000005</v>
       </c>
-      <c r="C7" s="6">
-        <v>395518.70480000012</v>
+      <c r="C7" s="5">
+        <v>298731.41599999997</v>
       </c>
-      <c r="D7" s="6">
-        <v>0.64732411061103523</v>
+      <c r="D7" s="5">
+        <v>0.49492379331144348</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
+      <c r="A8" s="3" t="s">
+        <v>27</v>
       </c>
-      <c r="B8" s="6">
-        <v>420185.32899999985</v>
+      <c r="B8" s="5">
+        <v>573200.74360000005</v>
       </c>
-      <c r="C8" s="6">
-        <v>321462.359</v>
+      <c r="C8" s="5">
+        <v>449128.29360000009</v>
       </c>
-      <c r="D8" s="6">
-        <v>0.62354295519377356</v>
+      <c r="D8" s="5">
+        <v>0.62083283533614164</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1920809.3479999998</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1474211.1780000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.62356556552047815</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5">
+        <v>410143.26149999996</v>
+      </c>
+      <c r="C10" s="5">
+        <v>302771.12150000007</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.55652151687548412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="5">
+        <v>586817.53269999998</v>
+      </c>
+      <c r="C11" s="5">
+        <v>454458.99270000012</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.65342835477270822</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <v>503663.22480000008</v>
+      </c>
+      <c r="C12" s="5">
+        <v>395518.70480000012</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.64732411061103523</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="5">
+        <v>420185.32899999985</v>
+      </c>
+      <c r="C13" s="5">
+        <v>321462.359</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.62354295519377356</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B14" s="5">
         <v>1855993.2324999997</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C14" s="5">
         <v>1397269.1824999989</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D14" s="5">
         <v>0.622557092498775</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B15" s="5">
         <v>300592.43749999994</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C15" s="5">
         <v>227548.54749999993</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D15" s="5">
         <v>0.65729784301298644</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B16" s="5">
         <v>344610.61260000005</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C16" s="5">
         <v>264966.78259999998</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D16" s="5">
         <v>0.63913518300210714</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B17" s="5">
         <v>217874.65679999994</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C17" s="5">
         <v>151012.14679999999</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D17" s="5">
         <v>0.56079947919556417</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B18" s="5">
         <v>448811.14930000005</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C18" s="5">
         <v>342405.55930000014</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D18" s="5">
         <v>0.64931403655826769</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B19" s="5">
         <v>544104.3763</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C19" s="5">
         <v>411336.14629999991</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D19" s="5">
         <v>0.60836722922378239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6">
-        <v>2163307.7248999993</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1682986.8349000006</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.60108244336540084</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="6">
-        <v>520097.44449999998</v>
-      </c>
-      <c r="C16" s="6">
-        <v>409532.86449999997</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.6452731666056164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="6">
-        <v>670579.78079999995</v>
-      </c>
-      <c r="C17" s="6">
-        <v>525594.26080000005</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.62905170690821843</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="6">
-        <v>399429.75600000005</v>
-      </c>
-      <c r="C18" s="6">
-        <v>298731.41599999997</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.49492379331144348</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="6">
-        <v>573200.74360000005</v>
-      </c>
-      <c r="C19" s="6">
-        <v>449128.29360000009</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.62083283533614164</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>5940110.3054000027</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>4554467.1954000024</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>0.61528078656628593</v>
       </c>
     </row>
@@ -37758,10 +37718,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>2.3026315789473683E-2</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>-9.5714285714285712</v>
       </c>
     </row>
@@ -37769,10 +37729,10 @@
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>0.24451754385964913</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>5.8744394618834077</v>
       </c>
     </row>
@@ -37780,10 +37740,10 @@
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>0.22368421052631579</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>1.3186274509803921</v>
       </c>
     </row>
@@ -37791,10 +37751,10 @@
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>0.24342105263157895</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>2.7837837837837838</v>
       </c>
     </row>
@@ -37802,10 +37762,10 @@
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>0.26535087719298245</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>3.4049586776859506</v>
       </c>
     </row>
@@ -37813,10 +37773,10 @@
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>3.0921052631578947</v>
       </c>
     </row>
@@ -37860,71 +37820,71 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
-      <c r="B4" s="6">
-        <v>1406891.9992999998</v>
+      <c r="B4" s="5">
+        <v>1672333.682100001</v>
       </c>
-      <c r="C4" s="6">
-        <v>1086722.4092999997</v>
+      <c r="C4" s="5">
+        <v>1290546.1521000005</v>
       </c>
-      <c r="D4" s="6">
-        <v>0.61288817581287414</v>
+      <c r="D4" s="5">
+        <v>0.60305843557680361</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
-      <c r="B5" s="6">
-        <v>1319591.7918999994</v>
+      <c r="B5" s="5">
+        <v>1541292.8321</v>
       </c>
-      <c r="C5" s="6">
-        <v>1018924.5818999999</v>
+      <c r="C5" s="5">
+        <v>1158274.0521000002</v>
       </c>
-      <c r="D5" s="6">
-        <v>0.65818123091367797</v>
+      <c r="D5" s="5">
+        <v>0.59343268259612658</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
-      <c r="B6" s="6">
-        <v>1541292.8321</v>
+      <c r="B6" s="5">
+        <v>1406891.9992999998</v>
       </c>
-      <c r="C6" s="6">
-        <v>1158274.0521000002</v>
+      <c r="C6" s="5">
+        <v>1086722.4092999997</v>
       </c>
-      <c r="D6" s="6">
-        <v>0.59343268259612658</v>
+      <c r="D6" s="5">
+        <v>0.61288817581287414</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
-      <c r="B7" s="6">
-        <v>1672333.682100001</v>
+      <c r="B7" s="5">
+        <v>1319591.7918999994</v>
       </c>
-      <c r="C7" s="6">
-        <v>1290546.1521000005</v>
+      <c r="C7" s="5">
+        <v>1018924.5818999999</v>
       </c>
-      <c r="D7" s="6">
-        <v>0.60305843557680361</v>
+      <c r="D7" s="5">
+        <v>0.65818123091367797</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>5940110.3054000027</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>4554467.195399994</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>0.61528078656628682</v>
       </c>
     </row>
@@ -37972,16 +37932,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>19</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <v>25</v>
       </c>
     </row>
@@ -37989,16 +37949,16 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>30</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>149</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>45</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <v>224</v>
       </c>
     </row>
@@ -38006,16 +37966,16 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>48</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>129</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>37</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>214</v>
       </c>
     </row>
@@ -38023,16 +37983,16 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>35</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>153</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>37</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>225</v>
       </c>
     </row>
@@ -38040,16 +38000,16 @@
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>30</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>154</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>40</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>224</v>
       </c>
     </row>
@@ -38057,16 +38017,16 @@
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>145</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>604</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>163</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>912</v>
       </c>
     </row>
@@ -38108,142 +38068,142 @@
       <c r="A4" s="2">
         <v>2024</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>4795278.0137</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>318011.51419999992</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>546029.80079999997</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>377051.7905</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>379760.02399999998</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>429673.41899999999</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>478534.79299999995</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>414118.03940000013</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>345384.408</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>428245.14779999992</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>10</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>486248.46300000005</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>11</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>262414.01770000003</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>12</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>329806.59630000003</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>41</v>
       </c>
     </row>
@@ -38251,142 +38211,142 @@
       <c r="A17" s="2">
         <v>2025</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>4213144.8307999987</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17">
         <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>401170.73329999991</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18">
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>2</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>598551.20450000011</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>3</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>459139.48599999998</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>4</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>410229.66850000003</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>5</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>327325.62400000007</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22">
         <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>6</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>357980.61450000003</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>7</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>418962.01720000012</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24">
         <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>8</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>555998.26700000011</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>9</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>410809.20450000005</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>10</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>169689.55699999997</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="A28" s="3">
         <v>11</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>62995.294800000003</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28">
         <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="A29" s="3">
         <v>12</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>40293.159500000009</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29">
         <v>5</v>
       </c>
     </row>
@@ -38394,10 +38354,10 @@
       <c r="A30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>9008422.8445000164</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30">
         <v>912</v>
       </c>
     </row>
@@ -38433,7 +38393,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>4</v>
       </c>
     </row>
@@ -38441,7 +38401,7 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>45</v>
       </c>
     </row>
@@ -38449,7 +38409,7 @@
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>37</v>
       </c>
     </row>
@@ -38457,7 +38417,7 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>37</v>
       </c>
     </row>
@@ -38465,7 +38425,7 @@
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>40</v>
       </c>
     </row>
@@ -38473,7 +38433,7 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>163</v>
       </c>
     </row>
